--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCC215A-DBE4-4AA7-81D7-8F893F47D22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526F8DA-47A0-4AE1-AE74-7BC9D4025768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526F8DA-47A0-4AE1-AE74-7BC9D4025768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F9D6B5-8857-40CC-AC49-DB580FFA6153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F9D6B5-8857-40CC-AC49-DB580FFA6153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FEE928-7E51-4113-822A-195BFC3B25E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FEE928-7E51-4113-822A-195BFC3B25E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA15A6E8-5035-414C-9825-F4B286098705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA15A6E8-5035-414C-9825-F4B286098705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE80A4E4-C0F1-41EC-B370-43E359E0D4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE80A4E4-C0F1-41EC-B370-43E359E0D4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCAFCE9-1863-43E9-9154-FD7D21E07C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 4.xlsx
+++ b/liste groupe 4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCAFCE9-1863-43E9-9154-FD7D21E07C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E2AEE4-097B-41F0-BDE5-999FECA1A010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
